--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N71_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N71_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.632382289085</v>
+        <v>13.42776212197631</v>
       </c>
       <c r="D2" t="n">
-        <v>83.84452945545104</v>
+        <v>13.62473603651079</v>
       </c>
       <c r="E2" t="n">
-        <v>26.34990466667078</v>
+        <v>4.281859508334001</v>
       </c>
       <c r="F2" t="n">
-        <v>27.16043554158646</v>
+        <v>4.4135707755078</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>0.8125</v>
       </c>
       <c r="D3" t="n">
-        <v>3.605551275463989</v>
+        <v>0.5859020822628983</v>
       </c>
       <c r="E3" t="n">
-        <v>26.34990466667078</v>
+        <v>4.281859508334001</v>
       </c>
       <c r="F3" t="n">
-        <v>27.16043554158646</v>
+        <v>4.4135707755078</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.19829856319925</v>
+        <v>1.982223516519878</v>
       </c>
       <c r="D4" t="n">
-        <v>10.60852564339318</v>
+        <v>1.723885417051391</v>
       </c>
       <c r="E4" t="n">
-        <v>26.34990466667078</v>
+        <v>4.281859508334001</v>
       </c>
       <c r="F4" t="n">
-        <v>27.16043554158646</v>
+        <v>4.4135707755078</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.63446379948248</v>
+        <v>6.278100367415903</v>
       </c>
       <c r="D5" t="n">
-        <v>37.53338649843385</v>
+        <v>6.099175305995501</v>
       </c>
       <c r="E5" t="n">
-        <v>26.34990466667078</v>
+        <v>4.281859508334001</v>
       </c>
       <c r="F5" t="n">
-        <v>27.16043554158646</v>
+        <v>4.4135707755078</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.29912705615568</v>
+        <v>5.736108146625297</v>
       </c>
       <c r="D6" t="n">
-        <v>35.37921171449629</v>
+        <v>5.749121903605647</v>
       </c>
       <c r="E6" t="n">
-        <v>26.34990466667078</v>
+        <v>4.281859508334001</v>
       </c>
       <c r="F6" t="n">
-        <v>27.16043554158646</v>
+        <v>4.4135707755078</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.35327871453641</v>
+        <v>9.482407791112166</v>
       </c>
       <c r="D7" t="n">
-        <v>57.59876491453348</v>
+        <v>9.359799298611691</v>
       </c>
       <c r="E7" t="n">
-        <v>26.34990466667078</v>
+        <v>4.281859508334001</v>
       </c>
       <c r="F7" t="n">
-        <v>27.16043554158646</v>
+        <v>4.4135707755078</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
